--- a/astro-site/public/dl/restaurant-checklist-templates/06-event-holiday-checklists.xlsx
+++ b/astro-site/public/dl/restaurant-checklist-templates/06-event-holiday-checklists.xlsx
@@ -839,7 +839,7 @@
     <row r="28" ht="31" customHeight="1">
       <c r="B28" s="30" t="inlineStr">
         <is>
-          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the FRAME of the day.</t>
+          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the BACKBONE of the day.</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Store furniture in storage</t>
+          <t>Move the furniture into storage</t>
         </is>
       </c>
       <c r="C15" s="36" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Take down and store the outdoor heaters if the patio is closed in winter</t>
+          <t>If the patio is closed in winter, store the heaters; propane tanks disconnected and kept outdoors in a locked cage, never inside</t>
         </is>
       </c>
       <c r="C17" s="36" t="inlineStr">
